--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלוש ציפורים דמיון חופשי</v>
+        <v>שלוש ציפורים – דמיון חופשי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-01</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלוש ציפורים דמיון חופשי</v>
+        <v>שלוש ציפורים – דמיון חופשי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלוש ציפורים – דמיון חופשי</v>
+        <v>בן שוקרון – יותר שמיים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%a9-%d7%a6%d7%99%d7%a4%d7%95%d7%a8%d7%99%d7%9d-%d7%93%d7%9e%d7%99%d7%95%d7%9f-%d7%97%d7%95%d7%a4%d7%a9%d7%99/</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%99%d7%95%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"דמיון חופשי” של יצחק קלפטר הוא מן השירים שבהם הפשטות הלירית נושאת על גבה עומק רגשי גדול. זהו שיר על אהבה שאינה מתממשת, על פער בין תשוקה למציאות, ועל המקום שבו הדמיון הופך למרחב מפלט – אך גם למרחב של</v>
+        <v>“יותר שמיים” של בן שוקרון הוא שיר אבל אישי שנשען על מציאות קשה, אך בוחר לבטא אותה דרך עדינות, שבריריות ואמונה, שירה מדוכדכת נרגשת ולא דרך זעם או פאתוס. הידיעה שהשיר נכתב בעקבות אובדן חבר קרוב במהלך אירוע צבאי בעזה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלוש ציפורים – דמיון חופשי</v>
+        <v>בן שוקרון – יותר שמיים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן שוקרון – יותר שמיים</v>
+        <v>טונה – הייתי שם</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%99%d7%95%d7%aa%d7%a8-%d7%a9%d7%9e%d7%99%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%a0%d7%94-%d7%94%d7%99%d7%99%d7%aa%d7%99-%d7%a9%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“יותר שמיים” של בן שוקרון הוא שיר אבל אישי שנשען על מציאות קשה, אך בוחר לבטא אותה דרך עדינות, שבריריות ואמונה, שירה מדוכדכת נרגשת ולא דרך זעם או פאתוס. הידיעה שהשיר נכתב בעקבות אובדן חבר קרוב במהלך אירוע צבאי בעזה</v>
+        <v>טונה מריץ ראפ אוטוביוגרפי שמבוסס על נרטיב של מאבק, התמדה וזהות. הוא משלב בין וידוי אישי לבין מסר אוניברסלי של הישרדות וצמיחה.הוא מציג את עצמו כ־ילד פריפריה שחולם על אימפריה – דמות שמגיעה ממקום מוחלש, חסר ביטחון וחסר משאבים, אך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן שוקרון – יותר שמיים</v>
+        <v>טונה – הייתי שם</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>טונה – הייתי שם</v>
+        <v>בניה ברבי – מהודו להודו</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%a0%d7%94-%d7%94%d7%99%d7%99%d7%aa%d7%99-%d7%a9%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%91%d7%a0%d7%99%d7%94-%d7%91%d7%a8%d7%91%d7%99-%d7%9e%d7%94%d7%95%d7%93%d7%95-%d7%9c%d7%94%d7%95%d7%93%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>טונה מריץ ראפ אוטוביוגרפי שמבוסס על נרטיב של מאבק, התמדה וזהות. הוא משלב בין וידוי אישי לבין מסר אוניברסלי של הישרדות וצמיחה.הוא מציג את עצמו כ־ילד פריפריה שחולם על אימפריה – דמות שמגיעה ממקום מוחלש, חסר ביטחון וחסר משאבים, אך</v>
+        <v>בניה ברבי שר שיר שמשתלב במסורת ישראלית מוכרת של שירי מסע – מסע גיאוגרפי, נפשי ורוחני – שבסופו מתגלה אמת פשוטה אך עוצמתית: מה שחיפשת רחוק, היה קרוב כל הזמן. כבר בבית הראשון מתוארת תבנית ישראלית כמעט קלאסית: תרמיל, מטוס,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>טונה – הייתי שם</v>
+        <v>בניה ברבי – מהודו להודו</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בניה ברבי – מהודו להודו</v>
+        <v>יסמין מועלם ומוש בן ארי – דרך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%a0%d7%99%d7%94-%d7%91%d7%a8%d7%91%d7%99-%d7%9e%d7%94%d7%95%d7%93%d7%95-%d7%9c%d7%94%d7%95%d7%93%d7%95/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a1%d7%9e%d7%99%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-%d7%95%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%93%d7%a8%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>בניה ברבי שר שיר שמשתלב במסורת ישראלית מוכרת של שירי מסע – מסע גיאוגרפי, נפשי ורוחני – שבסופו מתגלה אמת פשוטה אך עוצמתית: מה שחיפשת רחוק, היה קרוב כל הזמן. כבר בבית הראשון מתוארת תבנית ישראלית כמעט קלאסית: תרמיל, מטוס,</v>
+        <v>השיר "דרך" של מוש בן ארי הוא אחד משירי המסע האינטימיים והחשופים ביותר ברפרטואר שלו – מסע שאינו רק גיאוגרפי, אלא בראש ובראשונה רגשי. על רקע הביצוע החי המשותף עם יסמין מועלם באמפי שוני, מקבל השיר שכבה נוספת של עומק,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בניה ברבי – מהודו להודו</v>
+        <v>יסמין מועלם ומוש בן ארי – דרך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יסמין מועלם ומוש בן ארי – דרך</v>
+        <v>אניה בוקשטיין – רק עכשיו</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a1%d7%9e%d7%99%d7%9f-%d7%9e%d7%95%d7%a2%d7%9c%d7%9d-%d7%95%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%93%d7%a8%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a0%d7%99%d7%94-%d7%91%d7%95%d7%a7%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%a8%d7%a7-%d7%a2%d7%9b%d7%a9%d7%99%d7%95/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "דרך" של מוש בן ארי הוא אחד משירי המסע האינטימיים והחשופים ביותר ברפרטואר שלו – מסע שאינו רק גיאוגרפי, אלא בראש ובראשונה רגשי. על רקע הביצוע החי המשותף עם יסמין מועלם באמפי שוני, מקבל השיר שכבה נוספת של עומק,</v>
+        <v>אניה בוקשטיין שרה וידוי אישי עטוף בפופ קליט ומאיר, כזה שמצליח להיות גם קליל ומרקיד וגם חשוף ובוגר. המעבר המוזיקלי מסמבה שקטה ואקוסטית לפופ מידטמפו קצבי משקף במדויק את מהלך השיר: תנועה מהתבוננות פנימית ושברירית אל קבלה אופטימית וחיונית. הבית</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יסמין מועלם ומוש בן ארי – דרך</v>
+        <v>אניה בוקשטיין – רק עכשיו</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אניה בוקשטיין – רק עכשיו</v>
+        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a0%d7%99%d7%94-%d7%91%d7%95%d7%a7%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%a8%d7%a7-%d7%a2%d7%9b%d7%a9%d7%99%d7%95/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%95%d7%a2%d7%93%d7%95%d7%9f-%d7%94%d7%a7%d7%a6%d7%91-%d7%a9%d7%9c-%d7%90%d7%91%d7%99%d7%94%d7%95-%d7%a4%d7%a0%d7%97%d7%a1%d7%95%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93-%d7%9c%d7%a8%d7%a7/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אניה בוקשטיין שרה וידוי אישי עטוף בפופ קליט ומאיר, כזה שמצליח להיות גם קליל ומרקיד וגם חשוף ובוגר. המעבר המוזיקלי מסמבה שקטה ואקוסטית לפופ מידטמפו קצבי משקף במדויק את מהלך השיר: תנועה מהתבוננות פנימית ושברירית אל קבלה אופטימית וחיונית. הבית</v>
+        <v>איך להגדיר את המוסיקה? פאנק־סול ים־תיכוני עם הילולה בלקנית והפניית פנים לקהל? ואללה. נלך על זה. יש למישהו הגדרה אחרת למוסיקה של אביהו פנחסוב ומועדון הקצב שלו. מילים? כבר בשם השיר נמצא המפתח: זה קצב שמזמין תנועה וריקוד. המשפט החוזר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אניה בוקשטיין – רק עכשיו</v>
+        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
+        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%95%d7%a2%d7%93%d7%95%d7%9f-%d7%94%d7%a7%d7%a6%d7%91-%d7%a9%d7%9c-%d7%90%d7%91%d7%99%d7%94%d7%95-%d7%a4%d7%a0%d7%97%d7%a1%d7%95%d7%91-%d7%9c%d7%90-%d7%9e%d7%a4%d7%97%d7%93-%d7%9c%d7%a8%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%9c%d7%90%d7%94-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9c-%d7%90%d7%9e%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>איך להגדיר את המוסיקה? פאנק־סול ים־תיכוני עם הילולה בלקנית והפניית פנים לקהל? ואללה. נלך על זה. יש למישהו הגדרה אחרת למוסיקה של אביהו פנחסוב ומועדון הקצב שלו. מילים? כבר בשם השיר נמצא המפתח: זה קצב שמזמין תנועה וריקוד. המשפט החוזר</v>
+        <v>על אמת“ של לאה שבת עם "המשקפיים של נויפלד“ הוא דוגמה מובהקת ליצירה שמחברת בין פשטות ישירה לבין עומק רגשי, בין עייפות קיומית לבין תקווה עיקשת. השיר נפתח בהצהרה חשופה: – "אני קצת עייפה / מימים עצובים ולילות בלי שינה“.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מועדון הקצב של אביהו פנחסוב – לא מפחד לרקוד</v>
+        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
+        <v>שירי מימון – חמצן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%9c%d7%90%d7%94-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9c-%d7%90%d7%9e%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%99-%d7%9e%d7%99%d7%9e%d7%95%d7%9f-%d7%97%d7%9e%d7%a6%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>על אמת“ של לאה שבת עם "המשקפיים של נויפלד“ הוא דוגמה מובהקת ליצירה שמחברת בין פשטות ישירה לבין עומק רגשי, בין עייפות קיומית לבין תקווה עיקשת. השיר נפתח בהצהרה חשופה: – "אני קצת עייפה / מימים עצובים ולילות בלי שינה“.</v>
+        <v>"חמצן“ פועל במרחב שבין בלדה אישית לבין הצהרה דורית, ובכך מצליח להיות גם אינטימי מאוד וגם רחב-היקף. שירי מימון אינה מתייחסת לאירוע ספציפי, אלא מצב מתמשך: "את לא מבינה למה אין לך אוויר“, "הראש כבד וקצת קשה לנשום“. אלה תיאורים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>המשקפיים של נויפלד עם לאה שבת – על אמת</v>
+        <v>שירי מימון – חמצן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירי מימון – חמצן</v>
+        <v>עדן חסון – חוזר לעצמי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%99-%d7%9e%d7%99%d7%9e%d7%95%d7%9f-%d7%97%d7%9e%d7%a6%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%a2%d7%a6%d7%9e%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"חמצן“ פועל במרחב שבין בלדה אישית לבין הצהרה דורית, ובכך מצליח להיות גם אינטימי מאוד וגם רחב-היקף. שירי מימון אינה מתייחסת לאירוע ספציפי, אלא מצב מתמשך: "את לא מבינה למה אין לך אוויר“, "הראש כבד וקצת קשה לנשום“. אלה תיאורים</v>
+        <v>השיר ממשיך ומעמיק את הקו האישי־ווידויי מה שנפתח באופן מובהק ב־"אדם שבור“ –  כתיבה על שבר פנימי שקט, לא דרמטי-מתפרץ אלא יומיומי, מצטבר, אנושי מאוד. הבית הראשון מציג רשימת פעולות פשוטות: "עוד סיגריה במרפסת, שבע קפה שחור“, "מים חמים על</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירי מימון – חמצן</v>
+        <v>עדן חסון – חוזר לעצמי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן חסון – חוזר לעצמי</v>
+        <v>משה פרץ – ימים טובים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%a2%d7%a6%d7%9e%d7%99/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%9e%d7%99%d7%9d-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר ממשיך ומעמיק את הקו האישי־ווידויי מה שנפתח באופן מובהק ב־"אדם שבור“ –  כתיבה על שבר פנימי שקט, לא דרמטי-מתפרץ אלא יומיומי, מצטבר, אנושי מאוד. הבית הראשון מציג רשימת פעולות פשוטות: "עוד סיגריה במרפסת, שבע קפה שחור“, "מים חמים על</v>
+        <v>"ימים טובים" של משה פרץ משתייך לקו המוכר שלו: פופ-מיינסטרים מלודי, רגשי, נגיש מאוד, עם שילוב בין כאב אישי לבין נחמה פשוטה ואופטימית. לב השיר עוסק ברעיון פשוט: המתנות הגדולות של החיים אינן בהכרח אירועים דרמטיים, אלא רגעים קטנים –</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן חסון – חוזר לעצמי</v>
+        <v>משה פרץ – ימים טובים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה פרץ – ימים טובים</v>
+        <v>איתי לוי – בשעות הבודדות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%9e%d7%99%d7%9d-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%9c%d7%95%d7%99-%d7%91%d7%a9%d7%a2%d7%95%d7%aa-%d7%94%d7%91%d7%95%d7%93%d7%93%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"ימים טובים" של משה פרץ משתייך לקו המוכר שלו: פופ-מיינסטרים מלודי, רגשי, נגיש מאוד, עם שילוב בין כאב אישי לבין נחמה פשוטה ואופטימית. לב השיר עוסק ברעיון פשוט: המתנות הגדולות של החיים אינן בהכרח אירועים דרמטיים, אלא רגעים קטנים –</v>
+        <v>השיר "בשעות הבודדות" של איתי לוי ממקם את עצמו בבירור בתוך אחד הנתיבים השחוקים ביותר של הז’אנר הים־תיכוני הישראלי: הגבר הפגוע, המובס, המתקרבן – מול אישה שעזבה, שותקת, ואחראית לכאבו. הנרטיב מוכר עד לעייפה: היא נטשה, הוא נשאר לבד, סובל,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה פרץ – ימים טובים</v>
+        <v>איתי לוי – בשעות הבודדות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי לוי – בשעות הבודדות</v>
+        <v>שמעון בוסקילה – מעליות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%9c%d7%95%d7%99-%d7%91%d7%a9%d7%a2%d7%95%d7%aa-%d7%94%d7%91%d7%95%d7%93%d7%93%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%9e%d7%a2%d7%9c%d7%99%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בשעות הבודדות" של איתי לוי ממקם את עצמו בבירור בתוך אחד הנתיבים השחוקים ביותר של הז’אנר הים־תיכוני הישראלי: הגבר הפגוע, המובס, המתקרבן – מול אישה שעזבה, שותקת, ואחראית לכאבו. הנרטיב מוכר עד לעייפה: היא נטשה, הוא נשאר לבד, סובל,</v>
+        <v>שמעון בוסקילה  שר מצב של בין געגוע חזק לבין ניסיון להתאפס. “רק התאפסתי לא התרגלתי” – חוסר יציבות רגשית, “שורף מגעגועים” – געגוע פיזי, כמעט כואב, “לטפס על הקירות” – חוסר שקט, עצבים, בדידות זה אדם שמתפקד ביום-יום (קם, שוטף</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי לוי – בשעות הבודדות</v>
+        <v>שמעון בוסקילה – מעליות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה – מעליות</v>
+        <v>הפטריקים הפרויקט של דודי לוי ואבטיפוס – מלאך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%9e%d7%a2%d7%9c%d7%99%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%93%d7%95%d7%93%d7%99-%d7%9c%d7%95%d7%99-%d7%95%d7%90%d7%91%d7%98%d7%99%d7%a4%d7%95%d7%a1-2/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שמעון בוסקילה  שר מצב של בין געגוע חזק לבין ניסיון להתאפס. “רק התאפסתי לא התרגלתי” – חוסר יציבות רגשית, “שורף מגעגועים” – געגוע פיזי, כמעט כואב, “לטפס על הקירות” – חוסר שקט, עצבים, בדידות זה אדם שמתפקד ביום-יום (קם, שוטף</v>
+        <v>"מלאך” של דודי לוי הוא טקסט לירי שמרחף בין אגדה לחלום שבור, ובביצוע המחודש עם הפטריקים, ההרמוניה מבליטה את מה שתמיד היה בו: יופי שקט עם סדק עמוק בפנים. המלאך מתואר כיצור חופשי, אבל החופש הזה מוגבל: "מלאך נוגה מביט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה – מעליות</v>
+        <v>הפטריקים הפרויקט של דודי לוי ואבטיפוס – מלאך</v>
       </c>
     </row>
   </sheetData>
